--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -715,26 +715,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>900</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>1400</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>8000</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>16100</v>
       </c>
       <c r="F12" s="3">
         <v>8000</v>
@@ -945,7 +945,7 @@
         <v>16700</v>
       </c>
       <c r="E17" s="3">
-        <v>7400</v>
+        <v>20900</v>
       </c>
       <c r="F17" s="3">
         <v>32100</v>
@@ -970,26 +970,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-15800</v>
       </c>
       <c r="E18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-32100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-21700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-23800</v>
+        <v>-19500</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K18" s="3">
         <v>-20100</v>
@@ -1012,26 +1012,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
-        <v>4100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>900</v>
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>800</v>
@@ -1041,26 +1041,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-15100</v>
       </c>
       <c r="E21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-28700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-19700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-15600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-16800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-22400</v>
+        <v>-17800</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K21" s="3">
         <v>-18800</v>
@@ -1099,11 +1099,11 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-14800</v>
       </c>
       <c r="E23" s="3">
-        <v>-3300</v>
+        <v>-18200</v>
       </c>
       <c r="F23" s="3">
         <v>-29200</v>
@@ -1186,11 +1186,11 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-14800</v>
       </c>
       <c r="E26" s="3">
-        <v>-3300</v>
+        <v>-18200</v>
       </c>
       <c r="F26" s="3">
         <v>-29200</v>
@@ -1215,11 +1215,11 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-14800</v>
       </c>
       <c r="E27" s="3">
-        <v>-3300</v>
+        <v>-18200</v>
       </c>
       <c r="F27" s="3">
         <v>-29200</v>
@@ -1360,26 +1360,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-900</v>
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>-800</v>
@@ -1389,11 +1389,11 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-14800</v>
       </c>
       <c r="E33" s="3">
-        <v>-3300</v>
+        <v>-18200</v>
       </c>
       <c r="F33" s="3">
         <v>-29200</v>
@@ -1447,11 +1447,11 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-14800</v>
       </c>
       <c r="E35" s="3">
-        <v>-3300</v>
+        <v>-18200</v>
       </c>
       <c r="F35" s="3">
         <v>-29200</v>
@@ -1595,7 +1595,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -1740,7 +1740,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -2027,7 +2027,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="E59" s="3">
         <v>3200</v>
@@ -2113,8 +2113,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -2503,8 +2503,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>4</v>
+      <c r="D76" s="3">
+        <v>178400</v>
       </c>
       <c r="E76" s="3">
         <v>74600</v>
@@ -2595,11 +2595,11 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-14800</v>
       </c>
       <c r="E81" s="3">
-        <v>-3300</v>
+        <v>-18200</v>
       </c>
       <c r="F81" s="3">
         <v>-29200</v>
@@ -2641,7 +2641,7 @@
         <v>-400</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
@@ -2815,7 +2815,7 @@
         <v>17100</v>
       </c>
       <c r="E89" s="3">
-        <v>-6500</v>
+        <v>-42100</v>
       </c>
       <c r="F89" s="3">
         <v>-35600</v>
@@ -2854,22 +2854,22 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>-16900</v>
       </c>
       <c r="E94" s="3">
-        <v>18900</v>
+        <v>45400</v>
       </c>
       <c r="F94" s="3">
         <v>26500</v>
@@ -3156,11 +3156,11 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>138700</v>
       </c>
       <c r="E102" s="3">
-        <v>12300</v>
+        <v>3200</v>
       </c>
       <c r="F102" s="3">
         <v>-9100</v>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,62 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -719,16 +726,16 @@
         <v>900</v>
       </c>
       <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>900</v>
+      </c>
+      <c r="G8" s="3">
         <v>1400</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
+      <c r="H8" s="3">
+        <v>500</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
@@ -736,11 +743,17 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,8 +781,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -797,8 +816,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,37 +835,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>8000</v>
+        <v>13100</v>
       </c>
       <c r="E12" s="3">
-        <v>16100</v>
+        <v>8800</v>
       </c>
       <c r="F12" s="3">
         <v>8000</v>
       </c>
       <c r="G12" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I12" s="3">
         <v>15800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>11200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>11600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>16500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,26 +901,32 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>18000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -897,8 +936,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +971,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,54 +987,62 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F17" s="3">
         <v>16700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>20900</v>
       </c>
-      <c r="F17" s="3">
-        <v>32100</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I17" s="3">
         <v>21700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>17300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>18100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>23800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-15800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-19500</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
+      <c r="H18" s="3">
+        <v>-7700</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
@@ -991,11 +1050,17 @@
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,25 +1072,27 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>600</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1033,28 +1100,34 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-15100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-17800</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
+      <c r="H21" s="3">
+        <v>-6700</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1062,11 +1135,17 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,37 +1173,49 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-14800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-18200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-20200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-16100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-17300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1152,8 +1243,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-14800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-18200</v>
       </c>
-      <c r="F26" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I26" s="3">
         <v>-20200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-16100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-17300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-23000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-14800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-18200</v>
       </c>
-      <c r="F27" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-20200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-16100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-17300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-23000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,25 +1488,31 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3">
+        <v>-600</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -1381,40 +1520,52 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-14800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-18200</v>
       </c>
-      <c r="F33" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I33" s="3">
         <v>-20200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-16100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-17300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-23000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-14800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-18200</v>
       </c>
-      <c r="F35" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I35" s="3">
         <v>-20200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-16100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-17300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-23000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,78 +1702,92 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>329700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>132300</v>
+      </c>
+      <c r="F41" s="3">
         <v>157300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>62600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>48500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>57600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>59000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>54800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>71800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F42" s="3">
         <v>32600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>15000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>29700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>54400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>69300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>84600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>84800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1618,8 +1803,14 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1647,66 +1838,84 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>380900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>177500</v>
+      </c>
+      <c r="F46" s="3">
         <v>191500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>78600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>83400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>115600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>132100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>142000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>160200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1734,37 +1943,49 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
       <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
         <v>29300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>30200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>31300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>32400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1792,8 +2013,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,25 +2083,31 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G52" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1800</v>
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3">
         <v>1800</v>
@@ -1879,8 +2118,14 @@
       <c r="K52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>382500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>179400</v>
+      </c>
+      <c r="F54" s="3">
         <v>192500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>78600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>83400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>146600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>164100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>175100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>194400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,37 +2222,45 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2021,66 +2288,84 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F59" s="3">
         <v>11700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>12100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>10300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F60" s="3">
         <v>13100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>14500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2108,37 +2393,49 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>900</v>
+      </c>
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>26100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>27200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>28200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>29100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F66" s="3">
         <v>14100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>40700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>40100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>39400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>43200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-103200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-89400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-78900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-434500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-431200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-402000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-381900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-365800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-348500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>372700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>168900</v>
+      </c>
+      <c r="F76" s="3">
         <v>178400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>74600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>77500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>106000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>124000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>135700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>151200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-14800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-18200</v>
       </c>
-      <c r="F81" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I81" s="3">
         <v>-20200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-16100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-17300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-23000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,25 +3027,27 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>-400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
@@ -2661,8 +3058,14 @@
       <c r="K83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>500</v>
+      </c>
+      <c r="M83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="F89" s="3">
         <v>17100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-42100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-35600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-16700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-13800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-16900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-19700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,19 +3287,21 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -2869,16 +3310,22 @@
         <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3388,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-16900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>45400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>26500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>15200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>15200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-40100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3473,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,37 +3578,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>217800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F100" s="3">
         <v>138400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,33 +3648,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>197400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="F102" s="3">
         <v>138700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-16900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-59900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,90 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
-        <v>1400</v>
-      </c>
       <c r="H8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
@@ -749,11 +753,14 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +794,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,43 +850,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E12" s="3">
         <v>13100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8000</v>
       </c>
-      <c r="G12" s="3">
-        <v>16100</v>
-      </c>
       <c r="H12" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +924,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -921,15 +941,15 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>1900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -942,8 +962,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,64 +1015,68 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E17" s="3">
         <v>18700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16700</v>
       </c>
-      <c r="G17" s="3">
-        <v>20900</v>
-      </c>
       <c r="H17" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I17" s="3">
         <v>8200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-19500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-7700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1056,11 +1086,14 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,28 +1107,29 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1300</v>
       </c>
       <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="I20" s="3">
+        <v>600</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
@@ -1106,32 +1140,35 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10500</v>
       </c>
-      <c r="F21" s="3">
-        <v>-15100</v>
-      </c>
       <c r="G21" s="3">
-        <v>-17800</v>
+        <v>-14700</v>
       </c>
       <c r="H21" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6700</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1141,11 +1178,14 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,43 +1219,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-18200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-18200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I26" s="3">
         <v>-7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14800</v>
       </c>
-      <c r="G27" s="3">
-        <v>-18200</v>
-      </c>
       <c r="H27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,28 +1561,31 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1300</v>
       </c>
       <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
+      <c r="I32" s="3">
+        <v>-600</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
@@ -1526,46 +1596,52 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-18200</v>
-      </c>
       <c r="H33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I33" s="3">
         <v>-7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-18200</v>
-      </c>
       <c r="H35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I35" s="3">
         <v>-7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,93 +1790,100 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>314200</v>
+      </c>
+      <c r="E41" s="3">
         <v>329700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>132300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>157300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>62600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>57600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>54800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>71800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E42" s="3">
         <v>47300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>41400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>54400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>69300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>84600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>84800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1809,8 +1902,11 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1844,78 +1940,87 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>365700</v>
+      </c>
+      <c r="E46" s="3">
         <v>380900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>177500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>191500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>78600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>83400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>115600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>132100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>142000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>160200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1949,43 +2054,49 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>29300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,28 +2206,31 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1800</v>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>1800</v>
@@ -2124,8 +2244,11 @@
       <c r="M52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E54" s="3">
         <v>382500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>179400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>192500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>83400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>146600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>164100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>175100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>194400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,43 +2354,47 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2600</v>
+        <v>3700</v>
       </c>
       <c r="E57" s="3">
         <v>2600</v>
       </c>
       <c r="F57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2294,8 +2428,11 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2303,69 +2440,75 @@
         <v>6300</v>
       </c>
       <c r="E59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F59" s="3">
         <v>7000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2399,43 +2542,49 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>700</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
       <c r="H62" s="3">
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>26100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>27200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E66" s="3">
         <v>9800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-120800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-103200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-89400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-78900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-434500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-431200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-402000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-381900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-365800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-348500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>358200</v>
+      </c>
+      <c r="E76" s="3">
         <v>372700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>168900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>178400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>77500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>106000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>124000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>135700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>151200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-18200</v>
-      </c>
       <c r="H81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I81" s="3">
         <v>-7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3227,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3041,16 +3240,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>-400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
@@ -3064,8 +3263,11 @@
       <c r="M83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11900</v>
       </c>
-      <c r="F89" s="3">
-        <v>17100</v>
-      </c>
       <c r="G89" s="3">
-        <v>-42100</v>
+        <v>-10000</v>
       </c>
       <c r="H89" s="3">
+        <v>20600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-35600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-16700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,8 +3509,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3301,31 +3522,34 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16900</v>
       </c>
-      <c r="G94" s="3">
-        <v>45400</v>
-      </c>
       <c r="H94" s="3">
+        <v>18900</v>
+      </c>
+      <c r="I94" s="3">
         <v>26500</v>
-      </c>
-      <c r="I94" s="3">
-        <v>15200</v>
       </c>
       <c r="J94" s="3">
         <v>15200</v>
       </c>
       <c r="K94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +3827,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>217800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>138400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,39 +3903,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E102" s="3">
         <v>197400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25000</v>
       </c>
-      <c r="F102" s="3">
-        <v>138700</v>
-      </c>
       <c r="G102" s="3">
-        <v>3200</v>
+        <v>116900</v>
       </c>
       <c r="H102" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-9100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,97 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
@@ -756,11 +760,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,31 +804,34 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,46 +864,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E12" s="3">
         <v>18100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,13 +944,16 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -944,11 +964,11 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I14" s="3">
-        <v>18000</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -965,8 +985,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,70 +1042,74 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E17" s="3">
         <v>24100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17800</v>
       </c>
-      <c r="F18" s="3">
-        <v>-12900</v>
-      </c>
       <c r="G18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-15800</v>
       </c>
-      <c r="H18" s="3">
-        <v>-11700</v>
-      </c>
       <c r="I18" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-7700</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1089,11 +1119,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,31 +1141,32 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>4100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>600</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
@@ -1143,34 +1177,37 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-17600</v>
+        <v>-29900</v>
       </c>
       <c r="E21" s="3">
-        <v>-13700</v>
+        <v>-22300</v>
       </c>
       <c r="F21" s="3">
-        <v>-10500</v>
+        <v>-17900</v>
       </c>
       <c r="G21" s="3">
-        <v>-14700</v>
+        <v>-13000</v>
       </c>
       <c r="H21" s="3">
-        <v>-11500</v>
+        <v>-15800</v>
       </c>
       <c r="I21" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-11800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1181,34 +1218,37 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1222,69 +1262,75 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,31 +1631,34 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4600</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-4100</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>-2400</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-1000</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
@@ -1599,49 +1669,55 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,107 +1877,114 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E41" s="3">
         <v>314200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>329700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>157300</v>
       </c>
-      <c r="H41" s="3">
-        <v>62600</v>
-      </c>
       <c r="I41" s="3">
-        <v>48500</v>
+        <v>40300</v>
       </c>
       <c r="J41" s="3">
+        <v>23200</v>
+      </c>
+      <c r="K41" s="3">
         <v>57600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>71800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E42" s="3">
         <v>46500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>47300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>41400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32600</v>
       </c>
-      <c r="H42" s="3">
-        <v>15000</v>
-      </c>
       <c r="I42" s="3">
-        <v>29700</v>
+        <v>20800</v>
       </c>
       <c r="J42" s="3">
+        <v>42400</v>
+      </c>
+      <c r="K42" s="3">
         <v>54400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>69300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>84600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>84800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="I43" s="3">
+        <v>800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4500</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -1905,31 +1998,34 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1943,107 +2039,116 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3">
-        <v>5200</v>
+        <v>1200</v>
       </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>287500</v>
+      </c>
+      <c r="E46" s="3">
         <v>365700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>380900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>177500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191500</v>
       </c>
-      <c r="H46" s="3">
-        <v>78600</v>
-      </c>
       <c r="I46" s="3">
-        <v>83400</v>
+        <v>63300</v>
       </c>
       <c r="J46" s="3">
+        <v>70900</v>
+      </c>
+      <c r="K46" s="3">
         <v>115600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>132100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>142000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>160200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>61500</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2057,46 +2162,52 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J48" s="3">
+        <v>900</v>
+      </c>
+      <c r="K48" s="3">
         <v>29300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2133,8 +2244,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,31 +2326,34 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E52" s="3">
         <v>2600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+      <c r="I52" s="3">
+        <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>1800</v>
@@ -2247,8 +2367,11 @@
       <c r="N52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2408,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>354200</v>
+      </c>
+      <c r="E54" s="3">
         <v>369000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>382500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>179400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>192500</v>
       </c>
-      <c r="H54" s="3">
-        <v>78600</v>
-      </c>
       <c r="I54" s="3">
-        <v>83400</v>
+        <v>64300</v>
       </c>
       <c r="J54" s="3">
+        <v>71900</v>
+      </c>
+      <c r="K54" s="3">
         <v>146600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>164100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>175100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>194400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,69 +2485,73 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
-      </c>
-      <c r="E57" s="3">
-        <v>2600</v>
       </c>
       <c r="F57" s="3">
         <v>2600</v>
       </c>
       <c r="G57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2431,84 +2565,93 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6300</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>6300</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>7000</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>11700</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>4900</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>12100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E60" s="3">
         <v>10000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13100</v>
       </c>
-      <c r="H60" s="3">
-        <v>4000</v>
-      </c>
       <c r="I60" s="3">
-        <v>6000</v>
+        <v>6700</v>
       </c>
       <c r="J60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K60" s="3">
         <v>14500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2519,19 +2662,19 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2545,46 +2688,52 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>26100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2852,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E66" s="3">
         <v>10700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14100</v>
       </c>
-      <c r="H66" s="3">
-        <v>4000</v>
-      </c>
       <c r="I66" s="3">
-        <v>6000</v>
+        <v>7700</v>
       </c>
       <c r="J66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K66" s="3">
         <v>40700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2848,10 +3016,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3074,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-146000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-120800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-103200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-89400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-78900</v>
       </c>
-      <c r="H72" s="3">
-        <v>-434500</v>
-      </c>
       <c r="I72" s="3">
-        <v>-431200</v>
+        <v>-64100</v>
       </c>
       <c r="J72" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-402000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-381900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-365800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-348500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>337900</v>
+      </c>
+      <c r="E76" s="3">
         <v>358200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>372700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>168900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>178400</v>
       </c>
-      <c r="H76" s="3">
-        <v>74600</v>
-      </c>
       <c r="I76" s="3">
-        <v>77500</v>
+        <v>-61500</v>
       </c>
       <c r="J76" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="K76" s="3">
         <v>106000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>124000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>135700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>151200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,31 +3426,32 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3266,8 +3465,11 @@
       <c r="N83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10000</v>
       </c>
-      <c r="H89" s="3">
-        <v>20600</v>
-      </c>
       <c r="I89" s="3">
-        <v>-35600</v>
+        <v>-4700</v>
       </c>
       <c r="J89" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-16700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-16900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,8 +3730,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3525,31 +3746,34 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3851,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-259400</v>
+      </c>
+      <c r="E94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-16900</v>
-      </c>
       <c r="H94" s="3">
-        <v>18900</v>
+        <v>-11500</v>
       </c>
       <c r="I94" s="3">
-        <v>26500</v>
+        <v>21900</v>
       </c>
       <c r="J94" s="3">
-        <v>15200</v>
+        <v>18100</v>
       </c>
       <c r="K94" s="3">
         <v>15200</v>
       </c>
       <c r="L94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,31 +3911,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3716,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,69 +4073,75 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>217800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>138400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3906,42 +4155,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-280300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>197400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-25000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>116900</v>
       </c>
-      <c r="H102" s="3">
-        <v>34100</v>
-      </c>
       <c r="I102" s="3">
-        <v>-9100</v>
+        <v>17100</v>
       </c>
       <c r="J102" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-59900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,104 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
@@ -763,11 +766,14 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,35 +813,38 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -848,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,49 +877,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E12" s="3">
         <v>25500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,17 +963,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
@@ -988,8 +1007,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,76 +1068,80 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E17" s="3">
         <v>32100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-22200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1122,11 +1151,14 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,16 +1174,17 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1160,16 +1193,16 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
@@ -1180,38 +1213,41 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-17900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-15800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1221,11 +1257,14 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1250,8 +1289,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1265,49 +1304,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1332,8 +1377,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1347,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,16 +1700,19 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -1652,16 +1721,16 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
@@ -1672,52 +1741,58 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,117 +1963,124 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E41" s="3">
         <v>33700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>314200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>329700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>132300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>157300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>71800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>252400</v>
+      </c>
+      <c r="E42" s="3">
         <v>247500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>46500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>47300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>41400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>32600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>20800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>42400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>69300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>84600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>84800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
-      </c>
-      <c r="H43" s="3">
-        <v>800</v>
       </c>
       <c r="I43" s="3">
         <v>800</v>
       </c>
       <c r="J43" s="3">
+        <v>800</v>
+      </c>
+      <c r="K43" s="3">
         <v>4500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2001,35 +2093,38 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2042,13 +2137,16 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>400</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2062,79 +2160,85 @@
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>280900</v>
+      </c>
+      <c r="E46" s="3">
         <v>287500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>365700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>380900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>177500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>191500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>63300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>115600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>132100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>142000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>160200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E47" s="3">
         <v>61500</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2150,8 +2254,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2165,49 +2269,55 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2247,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,34 +2445,37 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E52" s="3">
         <v>4700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1800</v>
       </c>
       <c r="L52" s="3">
         <v>1800</v>
@@ -2370,8 +2489,11 @@
       <c r="O52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E54" s="3">
         <v>354200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>369000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>382500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>179400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>192500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>146600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>164100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>175100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>194400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,49 +2615,53 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
         <v>7600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2600</v>
       </c>
       <c r="G57" s="3">
         <v>2600</v>
       </c>
       <c r="H57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2536,7 +2669,7 @@
         <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
@@ -2554,7 +2687,7 @@
         <v>400</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2568,13 +2701,16 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
@@ -2595,90 +2731,96 @@
         <v>100</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E60" s="3">
         <v>15700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>300</v>
       </c>
       <c r="I61" s="3">
         <v>300</v>
       </c>
       <c r="J61" s="3">
+        <v>300</v>
+      </c>
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2691,8 +2833,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2717,23 +2862,26 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>26100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>27200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E66" s="3">
         <v>16400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3016,13 +3183,13 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>118000</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -3036,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-174400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-146000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-120800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-103200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-89400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-78900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-64100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-53000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-402000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-381900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-365800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-348500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>352500</v>
+      </c>
+      <c r="E76" s="3">
         <v>337900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>358200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>372700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>168900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>178400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-61500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-50800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>106000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>124000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>135700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>151200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,34 +3624,35 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
@@ -3468,8 +3666,11 @@
       <c r="O83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3749,11 +3969,11 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -3761,19 +3981,22 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-259400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>21900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>18100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>15200</v>
       </c>
       <c r="L94" s="3">
         <v>15200</v>
       </c>
       <c r="M94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3938,8 +4171,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3953,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>217800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>138400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2800</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4143,8 +4391,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4158,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-280300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>197400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>116900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-59900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
@@ -769,11 +773,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,38 +823,41 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E12" s="3">
         <v>26400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,25 +983,28 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>-500</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,82 +1095,86 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E17" s="3">
         <v>33200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-22200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1154,11 +1184,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,19 +1208,20 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
@@ -1196,16 +1230,16 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
@@ -1216,41 +1250,44 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-29900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1260,11 +1297,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1292,8 +1332,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1307,52 +1347,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1380,8 +1426,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,19 +1770,22 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
@@ -1724,16 +1794,16 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
@@ -1744,55 +1814,61 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,126 +2050,133 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E41" s="3">
         <v>22800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>314200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>329700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>132300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>157300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>57600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>59000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>253100</v>
+      </c>
+      <c r="E42" s="3">
         <v>252400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>247500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>46500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>47300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>32600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>42400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>69300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>84600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>84800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>800</v>
       </c>
       <c r="J43" s="3">
         <v>800</v>
       </c>
       <c r="K43" s="3">
+        <v>800</v>
+      </c>
+      <c r="L43" s="3">
         <v>4500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2096,38 +2189,41 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E44" s="3">
         <v>3000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2140,16 +2236,19 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="E45" s="3">
+        <v>400</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -2163,85 +2262,91 @@
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E46" s="3">
         <v>280900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>287500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>365700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>380900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>177500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>191500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>63300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>115600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>132100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>142000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>160200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E47" s="3">
         <v>81700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>61500</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2257,8 +2362,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2272,52 +2377,58 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,37 +2565,40 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E52" s="3">
         <v>9600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1800</v>
       </c>
       <c r="M52" s="3">
         <v>1800</v>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>348600</v>
+      </c>
+      <c r="E54" s="3">
         <v>374000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>354200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>369000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>382500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>179400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>192500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>164100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>175100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>194400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,63 +2746,67 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2600</v>
       </c>
       <c r="H57" s="3">
         <v>2600</v>
       </c>
       <c r="I57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
         <v>400</v>
@@ -2690,7 +2824,7 @@
         <v>400</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2704,8 +2838,11 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2713,7 +2850,7 @@
         <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -2734,66 +2871,72 @@
         <v>100</v>
       </c>
       <c r="L59" s="3">
+        <v>100</v>
+      </c>
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2801,29 +2944,29 @@
         <v>1200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>300</v>
       </c>
       <c r="J61" s="3">
         <v>300</v>
       </c>
       <c r="K61" s="3">
+        <v>300</v>
+      </c>
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2836,8 +2979,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2865,23 +3011,26 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>26100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E66" s="3">
         <v>21500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3186,13 +3354,13 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>118000</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-203900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-174400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-146000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-120800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-103200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-89400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-78900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-64100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-53000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-402000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-381900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-365800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-348500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>328600</v>
+      </c>
+      <c r="E76" s="3">
         <v>352500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>337900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>358200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>372700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>168900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>178400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-61500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-50800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>106000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>124000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>135700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>151200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,28 +3833,28 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-16700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4171,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3972,11 +4193,11 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -3984,19 +4205,22 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-259400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>21900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>18100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>15200</v>
       </c>
       <c r="M94" s="3">
         <v>15200</v>
       </c>
       <c r="N94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4174,8 +4408,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4564,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>39700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>217800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>138400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2800</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4394,8 +4643,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-280300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>197400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>116900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,117 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
@@ -776,11 +780,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,41 +833,44 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E12" s="3">
         <v>27000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,29 +1003,32 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,88 +1122,92 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E17" s="3">
         <v>34300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-31900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-22200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1187,11 +1217,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1218,13 +1252,13 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
@@ -1233,16 +1267,16 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
@@ -1253,44 +1287,47 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-33300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-29900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1300,11 +1337,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1335,8 +1375,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1350,55 +1390,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1429,8 +1475,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1782,13 +1852,13 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
@@ -1797,16 +1867,16 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
@@ -1817,58 +1887,64 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,135 +2137,142 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E41" s="3">
         <v>10100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>314200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>329700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>157300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>57600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>59000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>71800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>244200</v>
+      </c>
+      <c r="E42" s="3">
         <v>253100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>252400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>247500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>46500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>47300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>20800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>42400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>54400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>69300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>84600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>84800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>800</v>
       </c>
       <c r="K43" s="3">
         <v>800</v>
       </c>
       <c r="L43" s="3">
+        <v>800</v>
+      </c>
+      <c r="M43" s="3">
         <v>4500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2192,41 +2285,44 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3">
         <v>4300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -2239,19 +2335,22 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3">
+        <v>400</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
@@ -2265,91 +2364,97 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>263600</v>
+      </c>
+      <c r="E46" s="3">
         <v>271000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>280900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>287500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>365700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>380900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>177500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>70900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>115600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>132100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>142000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>160200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E47" s="3">
         <v>68300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>81700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>61500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2365,8 +2470,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2380,8 +2485,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2389,46 +2497,49 @@
         <v>1600</v>
       </c>
       <c r="E48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,40 +2685,43 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1800</v>
       </c>
       <c r="N52" s="3">
         <v>1800</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>326100</v>
+      </c>
+      <c r="E54" s="3">
         <v>348600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>374000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>354200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>369000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>382500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>179400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>192500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>164100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>175100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>194400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,55 +2877,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
         <v>8300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2600</v>
       </c>
       <c r="I57" s="3">
         <v>2600</v>
       </c>
       <c r="J57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2803,13 +2937,13 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
@@ -2827,7 +2961,7 @@
         <v>400</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2841,8 +2975,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2853,7 +2990,7 @@
         <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>100</v>
@@ -2874,102 +3011,108 @@
         <v>100</v>
       </c>
       <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E60" s="3">
         <v>17000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E61" s="3">
         <v>1200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>300</v>
       </c>
       <c r="K61" s="3">
         <v>300</v>
       </c>
       <c r="L61" s="3">
+        <v>300</v>
+      </c>
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2982,8 +3125,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3014,23 +3160,26 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>26100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E66" s="3">
         <v>20000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3357,13 +3525,13 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>118000</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-235500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-203900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-174400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-120800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-103200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-89400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-78900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-64100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-53000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-402000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-381900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-365800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-348500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>303100</v>
+      </c>
+      <c r="E76" s="3">
         <v>328600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>352500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>337900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>358200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>372700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>168900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>178400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-61500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-50800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>106000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>124000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>135700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>151200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,40 +4022,41 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4196,11 +4417,11 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -4208,19 +4429,22 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E94" s="3">
         <v>14800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-259400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>21900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>18100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>15200</v>
       </c>
       <c r="N94" s="3">
         <v>15200</v>
       </c>
       <c r="O94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4411,8 +4645,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>39700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>217800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>138400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2800</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4646,8 +4895,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-280300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>197400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>116900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-59900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,131 +656,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
@@ -790,11 +793,14 @@
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -846,47 +852,50 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
@@ -899,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E12" s="3">
         <v>32500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27000</v>
       </c>
-      <c r="G12" s="3">
-        <v>26400</v>
-      </c>
       <c r="H12" s="3">
+        <v>26500</v>
+      </c>
+      <c r="I12" s="3">
         <v>25500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,35 +1042,38 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G14" s="3">
-        <v>200</v>
       </c>
       <c r="H14" s="3">
         <v>-2600</v>
       </c>
       <c r="I14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J14" s="3">
         <v>-400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1079,8 +1098,11 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,100 +1175,104 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E17" s="3">
         <v>40700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-40300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-33200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-31900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-22200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1253,11 +1282,14 @@
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1309,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1286,19 +1319,19 @@
         <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
@@ -1307,16 +1340,16 @@
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
@@ -1327,50 +1360,53 @@
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-69900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-40600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-35000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-33300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-32200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-22300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1380,11 +1416,14 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1421,8 +1460,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1436,61 +1475,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-36800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1527,8 +1572,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1542,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-36800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-36800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +1979,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1922,19 +1991,19 @@
         <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
@@ -1943,16 +2012,16 @@
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
@@ -1963,64 +2032,70 @@
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-36800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-36800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,153 +2310,160 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E41" s="3">
         <v>56000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>314200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>329700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>157300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>57600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>54800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>71800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>353200</v>
+      </c>
+      <c r="E42" s="3">
         <v>346600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>244200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>253100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>252400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>247500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>46500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>47300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>41400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>32600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>20800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>42400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>54400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>69300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>84600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>84800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>5000</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>800</v>
       </c>
       <c r="M43" s="3">
         <v>800</v>
       </c>
       <c r="N43" s="3">
+        <v>800</v>
+      </c>
+      <c r="O43" s="3">
         <v>4500</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2384,47 +2476,50 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>700</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -2437,8 +2532,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2449,13 +2547,13 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>400</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
@@ -2469,103 +2567,109 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>409400</v>
+      </c>
+      <c r="E46" s="3">
         <v>413800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>263600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>271000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>280900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>287500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>365700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>380900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>177500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>191500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>63300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>70900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>115600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>132100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>142000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>160200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E47" s="3">
         <v>153300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>51700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>81700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>61800</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2581,8 +2685,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2596,61 +2700,67 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1600</v>
       </c>
       <c r="F48" s="3">
         <v>1600</v>
       </c>
       <c r="G48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>31300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2702,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,46 +2924,49 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E52" s="3">
         <v>8900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1800</v>
       </c>
       <c r="P52" s="3">
         <v>1800</v>
@@ -2861,8 +2980,11 @@
       <c r="S52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>530900</v>
+      </c>
+      <c r="E54" s="3">
         <v>577400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>326100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>348600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>374000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>354200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>369000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>382500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>179400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>192500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>71900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>146600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>164100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>175100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>194400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,66 +3138,70 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2600</v>
       </c>
       <c r="K57" s="3">
         <v>2600</v>
       </c>
       <c r="L57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
         <v>200</v>
@@ -3077,13 +3210,13 @@
         <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3">
         <v>400</v>
@@ -3101,7 +3234,7 @@
         <v>400</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3115,16 +3248,19 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
@@ -3133,7 +3269,7 @@
         <v>500</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="I59" s="3">
         <v>100</v>
@@ -3154,114 +3290,120 @@
         <v>100</v>
       </c>
       <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
         <v>12100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E60" s="3">
         <v>23900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="3">
         <v>1100</v>
       </c>
       <c r="F61" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G61" s="3">
         <v>1200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
-      </c>
-      <c r="L61" s="3">
-        <v>300</v>
       </c>
       <c r="M61" s="3">
         <v>300</v>
       </c>
       <c r="N61" s="3">
+        <v>300</v>
+      </c>
+      <c r="O61" s="3">
         <v>400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3416,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3312,23 +3457,26 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>26100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E66" s="3">
         <v>31000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>43200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3699,13 +3866,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>118000</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-336700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-272300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-235500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-203900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-174400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-146000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-120800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-103200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-89400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-64100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-53000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-402000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-381900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-365800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-348500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>493400</v>
+      </c>
+      <c r="E76" s="3">
         <v>546500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>303100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>328600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>352500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>337900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>358200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>372700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>168900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>178400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-61500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-50800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>106000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>124000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>135700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>151200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-36800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4249,19 +4447,19 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
@@ -4275,8 +4473,11 @@
       <c r="S83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,13 +4833,14 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -4644,11 +4864,11 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4656,19 +4876,22 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-201300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-259400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>18100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>15200</v>
       </c>
       <c r="P94" s="3">
         <v>15200</v>
       </c>
       <c r="Q94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4885,8 +5118,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E100" s="3">
         <v>274500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>39700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>217800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>138400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5150,8 +5398,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5165,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>42700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-280300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>197400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>116900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-59900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DNTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>DNTH</t>
   </si>
@@ -656,137 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
@@ -796,11 +800,14 @@
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,50 +862,53 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E12" s="3">
         <v>59900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,38 +1062,41 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-2600</v>
       </c>
       <c r="I14" s="3">
         <v>-2600</v>
       </c>
       <c r="J14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,106 +1202,110 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E17" s="3">
         <v>69800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-69500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-40300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1285,11 +1315,14 @@
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,31 +1343,32 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
       </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1343,16 +1377,16 @@
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
@@ -1363,53 +1397,56 @@
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-69900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-40600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-35000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-32200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-29900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-22300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1419,11 +1456,14 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1463,8 +1503,8 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-64400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-36800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1575,8 +1621,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-64400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-64400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,31 +2049,34 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
       </c>
       <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2015,16 +2085,16 @@
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
@@ -2035,67 +2105,73 @@
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-64400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-64400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,162 +2397,169 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>627700</v>
+      </c>
+      <c r="E41" s="3">
         <v>51100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>314200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>329700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>157300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>54800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>71800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>483600</v>
+      </c>
+      <c r="E42" s="3">
         <v>353200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>346600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>244200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>253100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>252400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>247500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>46500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>47300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>41400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>32600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>42400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>54400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>69300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>84600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>84800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5000</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>800</v>
       </c>
       <c r="N43" s="3">
         <v>800</v>
       </c>
       <c r="O43" s="3">
+        <v>800</v>
+      </c>
+      <c r="P43" s="3">
         <v>4500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2479,50 +2572,53 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E44" s="3">
         <v>3000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>700</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -2535,8 +2631,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2550,13 +2649,13 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="I45" s="3">
+        <v>400</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -2570,109 +2669,115 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1119900</v>
+      </c>
+      <c r="E46" s="3">
         <v>409400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>413800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>263600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>271000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>280900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>287500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>365700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>380900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>177500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>191500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>63300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>70900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>115600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>132100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>142000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>160200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E47" s="3">
         <v>110100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>153300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>51700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>81700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>61800</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2688,8 +2793,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2703,8 +2808,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2712,55 +2820,58 @@
         <v>1600</v>
       </c>
       <c r="E48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1600</v>
       </c>
       <c r="G48" s="3">
         <v>1600</v>
       </c>
       <c r="H48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>29300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>31300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>32400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,49 +3044,52 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E52" s="3">
         <v>9700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1800</v>
       </c>
       <c r="Q52" s="3">
         <v>1800</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1246900</v>
+      </c>
+      <c r="E54" s="3">
         <v>530900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>577400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>326100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>348600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>374000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>354200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>382500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>179400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>192500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>146600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>164100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>175100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>194400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3269,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>9700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2600</v>
       </c>
       <c r="L57" s="3">
         <v>2600</v>
       </c>
       <c r="M57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3204,7 +3338,7 @@
         <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -3213,13 +3347,13 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>300</v>
       </c>
       <c r="J58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>400</v>
@@ -3237,7 +3371,7 @@
         <v>400</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3251,19 +3385,22 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>500</v>
@@ -3272,7 +3409,7 @@
         <v>500</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -3293,78 +3430,84 @@
         <v>100</v>
       </c>
       <c r="P59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q59" s="3">
         <v>12100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E60" s="3">
         <v>30700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3372,41 +3515,41 @@
         <v>1000</v>
       </c>
       <c r="E61" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F61" s="3">
         <v>1100</v>
       </c>
       <c r="G61" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H61" s="3">
         <v>1200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
-      </c>
-      <c r="M61" s="3">
-        <v>300</v>
       </c>
       <c r="N61" s="3">
         <v>300</v>
       </c>
       <c r="O61" s="3">
+        <v>300</v>
+      </c>
+      <c r="P61" s="3">
         <v>400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3419,8 +3562,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3460,23 +3606,26 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>26100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>28200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>29100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E66" s="3">
         <v>37500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>43200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3869,13 +4037,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>118000</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-377600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-336700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-272300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-235500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-203900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-174400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-146000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-120800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-103200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-89400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-78900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-64100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-53000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-402000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-381900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-365800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-348500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-325600</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1201300</v>
+      </c>
+      <c r="E76" s="3">
         <v>493400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>546500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>303100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>328600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>352500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>337900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>358200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>372700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>178400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-61500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-50800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>106000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>124000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>135700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>151200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>172700</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-64400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4450,19 +4649,19 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-47000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-19700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,17 +5054,18 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -4867,11 +5088,11 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4879,19 +5100,22 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="E94" s="3">
         <v>37200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-201300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>14800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-259400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>21900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>18100</v>
-      </c>
-      <c r="P94" s="3">
-        <v>15200</v>
       </c>
       <c r="Q94" s="3">
         <v>15200</v>
       </c>
       <c r="R94" s="3">
+        <v>15200</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-40100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5121,8 +5355,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>739400</v>
+      </c>
+      <c r="E100" s="3">
         <v>4900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>274500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>39700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>217800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>138400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5401,8 +5650,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>576600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>42700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-280300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>197400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>116900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-59900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25900</v>
       </c>
     </row>
